--- a/2024AIDataScienceGNRGeneral/Advanced Excel/Jan18.xlsx
+++ b/2024AIDataScienceGNRGeneral/Advanced Excel/Jan18.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B00A91-C257-42AF-B600-5CE7870447A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BF2DA2-F05E-4837-8301-011099F25A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00C455A7-C27C-4F8F-95DF-8AE123A1D978}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
   <si>
     <t>First Name</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>Hi Heli,</t>
+  </si>
+  <si>
+    <t>Total (using =SUM)</t>
+  </si>
+  <si>
+    <t>Using (+)</t>
   </si>
 </sst>
 </file>
@@ -845,7 +851,7 @@
     <col min="14" max="14" width="4.88671875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="17.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -960,6 +966,54 @@
         <f>OR(D4=4, B4&gt;=10)</f>
         <v>1</v>
       </c>
+      <c r="H4" t="str">
+        <f>TEXT(A4, "yyyy")</f>
+        <v>2004</v>
+      </c>
+      <c r="I4" t="str">
+        <f>TEXT(A4, "yy")</f>
+        <v>04</v>
+      </c>
+      <c r="J4" t="str">
+        <f>TEXT(A4, "m")</f>
+        <v>2</v>
+      </c>
+      <c r="K4" t="str">
+        <f>TEXT(A4, "mm")</f>
+        <v>02</v>
+      </c>
+      <c r="L4" t="str">
+        <f>TEXT(A4, "mmm")</f>
+        <v>Feb</v>
+      </c>
+      <c r="M4" t="str">
+        <f>TEXT(A4, "mmmm")</f>
+        <v>February</v>
+      </c>
+      <c r="N4" t="str">
+        <f>TEXT(A4, "d")</f>
+        <v>19</v>
+      </c>
+      <c r="O4" t="str">
+        <f>TEXT(A4, "dd")</f>
+        <v>19</v>
+      </c>
+      <c r="P4" t="str">
+        <f>TEXT(A4, "ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="Q4" t="str">
+        <f>TEXT(A4, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="R4" t="str">
+        <f>TEXT(B4, "00")</f>
+        <v>33</v>
+      </c>
+      <c r="S4" t="str">
+        <f>TEXT(B4, "000")</f>
+        <v>033</v>
+      </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
@@ -988,6 +1042,54 @@
         <f t="shared" ref="G5:G18" si="4">OR(D5=4, B5&gt;=10)</f>
         <v>0</v>
       </c>
+      <c r="H5" t="str">
+        <f t="shared" ref="H5:H18" si="5">TEXT(A5, "yyyy")</f>
+        <v>2007</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" ref="I5:I18" si="6">TEXT(A5, "yy")</f>
+        <v>07</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" ref="J5:J18" si="7">TEXT(A5, "m")</f>
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" ref="K5:K18" si="8">TEXT(A5, "mm")</f>
+        <v>01</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" ref="L5:L18" si="9">TEXT(A5, "mmm")</f>
+        <v>Jan</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" ref="M5:M18" si="10">TEXT(A5, "mmmm")</f>
+        <v>January</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" ref="N5:N18" si="11">TEXT(A5, "d")</f>
+        <v>9</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" ref="O5:O18" si="12">TEXT(A5, "dd")</f>
+        <v>09</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" ref="P5:P18" si="13">TEXT(A5, "ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="Q5" t="str">
+        <f t="shared" ref="Q5:Q18" si="14">TEXT(A5, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="R5" t="str">
+        <f t="shared" ref="R5:R18" si="15">TEXT(B5, "00")</f>
+        <v>09</v>
+      </c>
+      <c r="S5" t="str">
+        <f t="shared" ref="S5:S18" si="16">TEXT(B5, "000")</f>
+        <v>009</v>
+      </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
@@ -1016,6 +1118,54 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
+      <c r="H6" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="O6" t="str">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="13"/>
+        <v>Sun</v>
+      </c>
+      <c r="Q6" t="str">
+        <f t="shared" si="14"/>
+        <v>Sunday</v>
+      </c>
+      <c r="R6" t="str">
+        <f t="shared" si="15"/>
+        <v>05</v>
+      </c>
+      <c r="S6" t="str">
+        <f t="shared" si="16"/>
+        <v>005</v>
+      </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -1044,6 +1194,54 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
+      <c r="H7" t="str">
+        <f t="shared" si="5"/>
+        <v>2010</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" si="13"/>
+        <v>Tue</v>
+      </c>
+      <c r="Q7" t="str">
+        <f t="shared" si="14"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="R7" t="str">
+        <f t="shared" si="15"/>
+        <v>05</v>
+      </c>
+      <c r="S7" t="str">
+        <f t="shared" si="16"/>
+        <v>005</v>
+      </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
@@ -1072,6 +1270,54 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
+      <c r="H8" t="str">
+        <f t="shared" si="5"/>
+        <v>2009</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="6"/>
+        <v>09</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="11"/>
+        <v>21</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="12"/>
+        <v>21</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="13"/>
+        <v>Tue</v>
+      </c>
+      <c r="Q8" t="str">
+        <f t="shared" si="14"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="R8" t="str">
+        <f t="shared" si="15"/>
+        <v>06</v>
+      </c>
+      <c r="S8" t="str">
+        <f t="shared" si="16"/>
+        <v>006</v>
+      </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
@@ -1100,6 +1346,54 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
+      <c r="H9" t="str">
+        <f t="shared" si="5"/>
+        <v>2006</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="6"/>
+        <v>06</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="11"/>
+        <v>22</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="12"/>
+        <v>22</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="13"/>
+        <v>Sat</v>
+      </c>
+      <c r="Q9" t="str">
+        <f t="shared" si="14"/>
+        <v>Saturday</v>
+      </c>
+      <c r="R9" t="str">
+        <f t="shared" si="15"/>
+        <v>09</v>
+      </c>
+      <c r="S9" t="str">
+        <f t="shared" si="16"/>
+        <v>009</v>
+      </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
@@ -1128,6 +1422,54 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
+      <c r="H10" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="11"/>
+        <v>23</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="12"/>
+        <v>23</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" si="13"/>
+        <v>Wed</v>
+      </c>
+      <c r="Q10" t="str">
+        <f t="shared" si="14"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="R10" t="str">
+        <f t="shared" si="15"/>
+        <v>06</v>
+      </c>
+      <c r="S10" t="str">
+        <f t="shared" si="16"/>
+        <v>006</v>
+      </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
@@ -1156,6 +1498,54 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="H11" t="str">
+        <f t="shared" si="5"/>
+        <v>2015</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="K11" t="str">
+        <f t="shared" si="8"/>
+        <v>05</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="9"/>
+        <v>May</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="10"/>
+        <v>May</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="11"/>
+        <v>24</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="12"/>
+        <v>24</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="13"/>
+        <v>Sun</v>
+      </c>
+      <c r="Q11" t="str">
+        <f t="shared" si="14"/>
+        <v>Sunday</v>
+      </c>
+      <c r="R11" t="str">
+        <f t="shared" si="15"/>
+        <v>03</v>
+      </c>
+      <c r="S11" t="str">
+        <f t="shared" si="16"/>
+        <v>003</v>
+      </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
@@ -1184,6 +1574,54 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
+      <c r="H12" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="9"/>
+        <v>Dec</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="10"/>
+        <v>December</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="11"/>
+        <v>25</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" si="12"/>
+        <v>25</v>
+      </c>
+      <c r="P12" t="str">
+        <f t="shared" si="13"/>
+        <v>Thu</v>
+      </c>
+      <c r="Q12" t="str">
+        <f t="shared" si="14"/>
+        <v>Thursday</v>
+      </c>
+      <c r="R12" t="str">
+        <f t="shared" si="15"/>
+        <v>66</v>
+      </c>
+      <c r="S12" t="str">
+        <f t="shared" si="16"/>
+        <v>066</v>
+      </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
@@ -1212,6 +1650,54 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="H13" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="K13" t="str">
+        <f t="shared" si="8"/>
+        <v>07</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="9"/>
+        <v>Jul</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" si="10"/>
+        <v>July</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="11"/>
+        <v>26</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="P13" t="str">
+        <f t="shared" si="13"/>
+        <v>Sat</v>
+      </c>
+      <c r="Q13" t="str">
+        <f t="shared" si="14"/>
+        <v>Saturday</v>
+      </c>
+      <c r="R13" t="str">
+        <f t="shared" si="15"/>
+        <v>07</v>
+      </c>
+      <c r="S13" t="str">
+        <f t="shared" si="16"/>
+        <v>007</v>
+      </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
@@ -1240,6 +1726,54 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
+      <c r="H14" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="8"/>
+        <v>04</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="9"/>
+        <v>Apr</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="10"/>
+        <v>April</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="11"/>
+        <v>26</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="P14" t="str">
+        <f t="shared" si="13"/>
+        <v>Sat</v>
+      </c>
+      <c r="Q14" t="str">
+        <f t="shared" si="14"/>
+        <v>Saturday</v>
+      </c>
+      <c r="R14" t="str">
+        <f t="shared" si="15"/>
+        <v>15</v>
+      </c>
+      <c r="S14" t="str">
+        <f t="shared" si="16"/>
+        <v>015</v>
+      </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
@@ -1268,6 +1802,54 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
+      <c r="H15" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="9"/>
+        <v>Dec</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="10"/>
+        <v>December</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="11"/>
+        <v>27</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="P15" t="str">
+        <f t="shared" si="13"/>
+        <v>Sat</v>
+      </c>
+      <c r="Q15" t="str">
+        <f t="shared" si="14"/>
+        <v>Saturday</v>
+      </c>
+      <c r="R15" t="str">
+        <f t="shared" si="15"/>
+        <v>10</v>
+      </c>
+      <c r="S15" t="str">
+        <f t="shared" si="16"/>
+        <v>010</v>
+      </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
@@ -1296,8 +1878,56 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H16" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="8"/>
+        <v>09</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="9"/>
+        <v>Sep</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" si="10"/>
+        <v>September</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="11"/>
+        <v>27</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="P16" t="str">
+        <f t="shared" si="13"/>
+        <v>Sat</v>
+      </c>
+      <c r="Q16" t="str">
+        <f t="shared" si="14"/>
+        <v>Saturday</v>
+      </c>
+      <c r="R16" t="str">
+        <f t="shared" si="15"/>
+        <v>04</v>
+      </c>
+      <c r="S16" t="str">
+        <f t="shared" si="16"/>
+        <v>004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>39688</v>
       </c>
@@ -1324,8 +1954,56 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="8"/>
+        <v>08</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="9"/>
+        <v>Aug</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="10"/>
+        <v>August</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="11"/>
+        <v>28</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="P17" t="str">
+        <f t="shared" si="13"/>
+        <v>Thu</v>
+      </c>
+      <c r="Q17" t="str">
+        <f t="shared" si="14"/>
+        <v>Thursday</v>
+      </c>
+      <c r="R17" t="str">
+        <f t="shared" si="15"/>
+        <v>13</v>
+      </c>
+      <c r="S17" t="str">
+        <f t="shared" si="16"/>
+        <v>013</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>39507</v>
       </c>
@@ -1352,24 +2030,86 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" t="str">
+        <f t="shared" si="5"/>
+        <v>2008</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="6"/>
+        <v>08</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="8"/>
+        <v>02</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="9"/>
+        <v>Feb</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" si="10"/>
+        <v>February</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="11"/>
+        <v>29</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="12"/>
+        <v>29</v>
+      </c>
+      <c r="P18" t="str">
+        <f t="shared" si="13"/>
+        <v>Fri</v>
+      </c>
+      <c r="Q18" t="str">
+        <f t="shared" si="14"/>
+        <v>Friday</v>
+      </c>
+      <c r="R18" t="str">
+        <f t="shared" si="15"/>
+        <v>07</v>
+      </c>
+      <c r="S18" t="str">
+        <f t="shared" si="16"/>
+        <v>007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="Q20" t="s">
+        <v>63</v>
+      </c>
+      <c r="R20">
+        <f>SUM(R4:R18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>47</v>
       </c>
       <c r="C21">
         <v>32</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="Q21" t="s">
+        <v>64</v>
+      </c>
+      <c r="R21">
+        <f>R17+R18</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>48</v>
       </c>
@@ -1378,12 +2118,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>47</v>
       </c>
@@ -1391,7 +2131,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>49</v>
       </c>
